--- a/projects/ecm-compute/v1.0.0/export/用户管理/用户管理_params.xlsx
+++ b/projects/ecm-compute/v1.0.0/export/用户管理/用户管理_params.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -563,7 +563,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>e_entity_adminId</t>
+          <t>e_entity_list_0_id</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -573,19 +573,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>${entity_adminId}</t>
+          <t>${entity_list_0_id}</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>由 获取当前用户信息 提取 (path: entity.adminId)</t>
+          <t>由 前置 API: list 提取 (path: entity.list[0].id)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>e_entity_countryCode</t>
+          <t>e_entity_list_0_tenantId</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -595,19 +595,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>${entity_countryCode}</t>
+          <t>${entity_list_0_tenantId}</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>由 获取当前用户信息 提取 (path: entity.countryCode)</t>
+          <t>由 前置 API: list 提取 (path: entity.list[0].tenantId)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>e_entity_id</t>
+          <t>e_entity_adminId</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -617,19 +617,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>${entity_id}</t>
+          <t>${entity_adminId}</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>由 获取当前用户信息 提取 (path: entity.id)</t>
+          <t>由 获取当前用户信息 提取 (path: entity.adminId)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>e_entity_tenantId</t>
+          <t>e_tenantId</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -639,7 +639,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>${entity_tenantId}</t>
+          <t>${tenantId}</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -651,7 +651,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>e_tenantId</t>
+          <t>e_adminId</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -661,19 +661,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>${tenantId}</t>
+          <t>${adminId}</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>由 获取当前用户信息 提取 (path: entity.tenantId)</t>
+          <t>由 获取当前用户信息 提取 (path: entity.id)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>e_adminId</t>
+          <t>e_name_userName</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -683,19 +683,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>${adminId}</t>
+          <t>${gen_unique_name('AT', gen_timestamp(), '...')}</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>由 获取当前用户信息 提取 (path: entity.id)</t>
+          <t>步骤 创建用户 的名称字段</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>e_entity_0_id</t>
+          <t>e_name_name</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -705,19 +705,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>${entity_0_id}</t>
+          <t>${gen_unique_name('AT', gen_timestamp(), '...')}</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>由 前置 API: display-by-role 提取 (path: entity[0].id)</t>
+          <t>步骤 创建用户 的名称字段</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>e_entity_userId</t>
+          <t>e_mutable_description</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -727,76 +727,10 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>${entity_userId}</t>
+          <t>${gen_mutable_value(gen_timestamp())}</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
-        <is>
-          <t>由 前置 API: reset 提取 (path: entity.userId)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>e_name_userName</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>${gen_unique_name('AT', gen_timestamp(), '...')}</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>步骤 创建用户 的名称字段</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>e_name_name</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>${gen_unique_name('AT', gen_timestamp(), '...')}</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>步骤 创建用户 的名称字段</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>e_mutable_description</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>${gen_mutable_value(gen_timestamp())}</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
         <is>
           <t>步骤 创建用户 的可变字段</t>
         </is>

--- a/projects/ecm-compute/v1.0.0/export/用户管理/用户管理_params.xlsx
+++ b/projects/ecm-compute/v1.0.0/export/用户管理/用户管理_params.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -563,7 +563,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>e_entity_list_0_id</t>
+          <t>e_entity_adminId</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -573,19 +573,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>${entity_list_0_id}</t>
+          <t>${entity_adminId}</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>由 前置 API: list 提取 (path: entity.list[0].id)</t>
+          <t>由 获取当前用户信息 提取 (path: entity.adminId)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>e_entity_list_0_tenantId</t>
+          <t>e_tenantId</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -595,19 +595,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>${entity_list_0_tenantId}</t>
+          <t>${tenantId}</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>由 前置 API: list 提取 (path: entity.list[0].tenantId)</t>
+          <t>由 获取当前用户信息 提取 (path: entity.tenantId)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>e_entity_adminId</t>
+          <t>e_adminId</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -617,19 +617,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>${entity_adminId}</t>
+          <t>${adminId}</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>由 获取当前用户信息 提取 (path: entity.adminId)</t>
+          <t>由 获取当前用户信息 提取 (path: entity.id)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>e_tenantId</t>
+          <t>e_name_userName</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -639,19 +639,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>${tenantId}</t>
+          <t>${gen_unique_name('AT', gen_timestamp(), '...')}</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>由 获取当前用户信息 提取 (path: entity.tenantId)</t>
+          <t>步骤 创建用户 的名称字段</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>e_adminId</t>
+          <t>e_name_name</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -661,19 +661,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>${adminId}</t>
+          <t>${gen_unique_name('AT', gen_timestamp(), '...')}</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>由 获取当前用户信息 提取 (path: entity.id)</t>
+          <t>步骤 创建用户 的名称字段</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>e_name_userName</t>
+          <t>e_mutable_description</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -683,54 +683,10 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>${gen_unique_name('AT', gen_timestamp(), '...')}</t>
+          <t>${gen_mutable_value(gen_timestamp())}</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
-        <is>
-          <t>步骤 创建用户 的名称字段</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>e_name_name</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>${gen_unique_name('AT', gen_timestamp(), '...')}</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>步骤 创建用户 的名称字段</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>e_mutable_description</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>${gen_mutable_value(gen_timestamp())}</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
         <is>
           <t>步骤 创建用户 的可变字段</t>
         </is>

--- a/projects/ecm-compute/v1.0.0/export/用户管理/用户管理_params.xlsx
+++ b/projects/ecm-compute/v1.0.0/export/用户管理/用户管理_params.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -585,7 +585,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>e_tenantId</t>
+          <t>e_entity_countryCode</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -595,19 +595,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>${tenantId}</t>
+          <t>${entity_countryCode}</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>由 获取当前用户信息 提取 (path: entity.tenantId)</t>
+          <t>由 获取当前用户信息 提取 (path: entity.countryCode)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>e_adminId</t>
+          <t>e_entity_tenantId</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -617,19 +617,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>${adminId}</t>
+          <t>${entity_tenantId}</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>由 获取当前用户信息 提取 (path: entity.id)</t>
+          <t>由 获取当前用户信息 提取 (path: entity.tenantId)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>e_name_userName</t>
+          <t>e_tenantId</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -639,19 +639,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>${gen_unique_name('AT', gen_timestamp(), '...')}</t>
+          <t>${tenantId}</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>步骤 创建用户 的名称字段</t>
+          <t>由 获取当前用户信息 提取 (path: entity.tenantId)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>e_name_name</t>
+          <t>e_adminId</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -661,32 +661,76 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>${gen_unique_name('AT', gen_timestamp(), '...')}</t>
+          <t>${adminId}</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>步骤 创建用户 的名称字段</t>
+          <t>由 获取当前用户信息 提取 (path: entity.id)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>e_name_userName</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>${gen_unique_name('AT', gen_timestamp(), '...')}</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>步骤 创建用户 的名称字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>e_name_name</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>${gen_unique_name('AT', gen_timestamp(), '...')}</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>步骤 创建用户 的名称字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>e_mutable_description</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>${gen_mutable_value(gen_timestamp())}</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>步骤 创建用户 的可变字段</t>
         </is>

--- a/projects/ecm-compute/v1.0.0/export/用户管理/用户管理_params.xlsx
+++ b/projects/ecm-compute/v1.0.0/export/用户管理/用户管理_params.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -563,7 +563,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>e_entity_adminId</t>
+          <t>e_entity_list_0_policyList_0_id</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -573,19 +573,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>${entity_adminId}</t>
+          <t>${entity_list_0_policyList_0_id}</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>由 获取当前用户信息 提取 (path: entity.adminId)</t>
+          <t>由 获取用户列表 提取 (path: entity.list[0].policyList[0].id)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>e_entity_countryCode</t>
+          <t>e_entity_list_0_tenantId</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -595,19 +595,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>${entity_countryCode}</t>
+          <t>${entity_list_0_tenantId}</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>由 获取当前用户信息 提取 (path: entity.countryCode)</t>
+          <t>由 获取用户列表 提取 (path: entity.list[0].tenantId)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>e_entity_tenantId</t>
+          <t>e_entity_adminId</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -617,19 +617,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>${entity_tenantId}</t>
+          <t>${entity_adminId}</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>由 获取当前用户信息 提取 (path: entity.tenantId)</t>
+          <t>由 获取当前用户信息 提取 (path: entity.adminId)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>e_tenantId</t>
+          <t>e_entity_countryCode</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -639,19 +639,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>${tenantId}</t>
+          <t>${entity_countryCode}</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>由 获取当前用户信息 提取 (path: entity.tenantId)</t>
+          <t>由 获取当前用户信息 提取 (path: entity.countryCode)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>e_adminId</t>
+          <t>e_tenantId</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -661,19 +661,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>${adminId}</t>
+          <t>${tenantId}</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>由 获取当前用户信息 提取 (path: entity.id)</t>
+          <t>由 获取当前用户信息 提取 (path: entity.tenantId)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>e_name_userName</t>
+          <t>e_adminId</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -683,19 +683,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>${gen_unique_name('AT', gen_timestamp(), '...')}</t>
+          <t>${adminId}</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>步骤 创建用户 的名称字段</t>
+          <t>由 获取当前用户信息 提取 (path: entity.id)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>e_name_name</t>
+          <t>e_entity_0_children_0_id</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -705,32 +705,76 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>${gen_unique_name('AT', gen_timestamp(), '...')}</t>
+          <t>${entity_0_children_0_id}</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>步骤 创建用户 的名称字段</t>
+          <t>由 前置 API: display-by-role 提取 (path: entity[0].children[0].id)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>e_name_userName</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>${gen_unique_name('AT', gen_timestamp(), '...')}</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>步骤 创建用户 的名称字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>e_name_name</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>${gen_unique_name('AT', gen_timestamp(), '...')}</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>步骤 创建用户 的名称字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>e_mutable_description</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>${gen_mutable_value(gen_timestamp())}</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>步骤 创建用户 的可变字段</t>
         </is>

--- a/projects/ecm-compute/v1.0.0/export/用户管理/用户管理_params.xlsx
+++ b/projects/ecm-compute/v1.0.0/export/用户管理/用户管理_params.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -651,7 +651,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>e_tenantId</t>
+          <t>e_entity_tenantId</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>${tenantId}</t>
+          <t>${entity_tenantId}</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>e_adminId</t>
+          <t>e_tenantId</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -683,19 +683,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>${adminId}</t>
+          <t>${tenantId}</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>由 获取当前用户信息 提取 (path: entity.id)</t>
+          <t>由 获取当前用户信息 提取 (path: entity.tenantId)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>e_entity_0_children_0_id</t>
+          <t>e_adminId</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -705,19 +705,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>${entity_0_children_0_id}</t>
+          <t>${adminId}</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>由 前置 API: display-by-role 提取 (path: entity[0].children[0].id)</t>
+          <t>由 获取当前用户信息 提取 (path: entity.id)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>e_name_userName</t>
+          <t>e_entity_0_children_0_id</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -727,19 +727,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>${gen_unique_name('AT', gen_timestamp(), '...')}</t>
+          <t>${entity_0_children_0_id}</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>步骤 创建用户 的名称字段</t>
+          <t>由 前置 API: display-by-role 提取 (path: entity[0].children[0].id)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>e_name_name</t>
+          <t>e_name_userName</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -761,20 +761,42 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>e_name_name</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>${gen_unique_name('AT', gen_timestamp(), '...')}</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>步骤 创建用户 的名称字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>e_mutable_description</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>${gen_mutable_value(gen_timestamp())}</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>步骤 创建用户 的可变字段</t>
         </is>

--- a/projects/ecm-compute/v1.0.0/export/用户管理/用户管理_params.xlsx
+++ b/projects/ecm-compute/v1.0.0/export/用户管理/用户管理_params.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -717,7 +717,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>e_entity_0_children_0_id</t>
+          <t>e_entity_id</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -727,19 +727,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>${entity_0_children_0_id}</t>
+          <t>${entity_id}</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>由 前置 API: display-by-role 提取 (path: entity[0].children[0].id)</t>
+          <t>由 前置 API: password-policy 提取 (path: entity.id)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>e_name_userName</t>
+          <t>e_entity_createdAt</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -749,19 +749,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>${gen_unique_name('AT', gen_timestamp(), '...')}</t>
+          <t>${entity_createdAt}</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>步骤 创建用户 的名称字段</t>
+          <t>由 前置 API: password-policy 提取 (path: entity.createdAt)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>e_name_name</t>
+          <t>e_entity_updatedAt</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -771,32 +771,76 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>${gen_unique_name('AT', gen_timestamp(), '...')}</t>
+          <t>${entity_updatedAt}</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>步骤 创建用户 的名称字段</t>
+          <t>由 前置 API: password-policy 提取 (path: entity.updatedAt)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>e_name_userName</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>${gen_unique_name('AT', gen_timestamp(), '...')}</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>步骤 创建用户 的名称字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>e_name_name</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>${gen_unique_name('AT', gen_timestamp(), '...')}</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>步骤 创建用户 的名称字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>e_mutable_description</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>${gen_mutable_value(gen_timestamp())}</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>步骤 创建用户 的可变字段</t>
         </is>

--- a/projects/ecm-compute/v1.0.0/export/用户管理/用户管理_params.xlsx
+++ b/projects/ecm-compute/v1.0.0/export/用户管理/用户管理_params.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -717,7 +717,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>e_entity_id</t>
+          <t>e_entity_0_id</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -727,19 +727,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>${entity_id}</t>
+          <t>${entity_0_id}</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>由 前置 API: password-policy 提取 (path: entity.id)</t>
+          <t>由 前置 API: display-by-role 提取 (path: entity[0].id)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>e_entity_createdAt</t>
+          <t>e_entity_id</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -749,19 +749,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>${entity_createdAt}</t>
+          <t>${entity_id}</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>由 前置 API: password-policy 提取 (path: entity.createdAt)</t>
+          <t>由 前置 API: password-policy 提取 (path: entity.id)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>e_entity_updatedAt</t>
+          <t>e_entity_createdAt</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -771,19 +771,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>${entity_updatedAt}</t>
+          <t>${entity_createdAt}</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>由 前置 API: password-policy 提取 (path: entity.updatedAt)</t>
+          <t>由 前置 API: password-policy 提取 (path: entity.createdAt)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>e_name_userName</t>
+          <t>e_entity_updatedAt</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -793,19 +793,19 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>${gen_unique_name('AT', gen_timestamp(), '...')}</t>
+          <t>${entity_updatedAt}</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>步骤 创建用户 的名称字段</t>
+          <t>由 前置 API: password-policy 提取 (path: entity.updatedAt)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>e_name_name</t>
+          <t>e_name_userName</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>${gen_unique_name('AT', gen_timestamp(), '...')}</t>
+          <t>${gen_test_name('userName')}</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -827,20 +827,42 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>e_name_name</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>${gen_test_name('name')}</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>步骤 创建用户 的名称字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>e_mutable_description</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>${gen_mutable_value(gen_timestamp())}</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>${gen_mutable_value()}</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>步骤 创建用户 的可变字段</t>
         </is>

--- a/projects/ecm-compute/v1.0.0/export/用户管理/用户管理_params.xlsx
+++ b/projects/ecm-compute/v1.0.0/export/用户管理/用户管理_params.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -563,7 +563,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>e_entity_list_0_policyList_0_id</t>
+          <t>e_entity_adminId</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -573,19 +573,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>${entity_list_0_policyList_0_id}</t>
+          <t>${entity_adminId}</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>由 获取用户列表 提取 (path: entity.list[0].policyList[0].id)</t>
+          <t>由 获取当前用户信息 提取 (path: entity.adminId)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>e_entity_list_0_tenantId</t>
+          <t>e_entity_countryCode</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -595,19 +595,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>${entity_list_0_tenantId}</t>
+          <t>${entity_countryCode}</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>由 获取用户列表 提取 (path: entity.list[0].tenantId)</t>
+          <t>由 获取当前用户信息 提取 (path: entity.countryCode)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>e_entity_adminId</t>
+          <t>e_entity_tenantId</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -617,19 +617,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>${entity_adminId}</t>
+          <t>${entity_tenantId}</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>由 获取当前用户信息 提取 (path: entity.adminId)</t>
+          <t>由 获取当前用户信息 提取 (path: entity.tenantId)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>e_entity_countryCode</t>
+          <t>e_entity_0_id</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -639,19 +639,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>${entity_countryCode}</t>
+          <t>${entity_0_id}</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>由 获取当前用户信息 提取 (path: entity.countryCode)</t>
+          <t>由 前置 API: display-by-role 提取 (path: entity[0].id)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>e_entity_tenantId</t>
+          <t>e_entity_id</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -661,19 +661,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>${entity_tenantId}</t>
+          <t>${entity_id}</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>由 获取当前用户信息 提取 (path: entity.tenantId)</t>
+          <t>由 前置 API: password-policy 提取 (path: entity.id)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>e_tenantId</t>
+          <t>e_entity_createdAt</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -683,19 +683,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>${tenantId}</t>
+          <t>${entity_createdAt}</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>由 获取当前用户信息 提取 (path: entity.tenantId)</t>
+          <t>由 前置 API: password-policy 提取 (path: entity.createdAt)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>e_adminId</t>
+          <t>e_entity_updatedAt</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -705,19 +705,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>${adminId}</t>
+          <t>${entity_updatedAt}</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>由 获取当前用户信息 提取 (path: entity.id)</t>
+          <t>由 前置 API: password-policy 提取 (path: entity.updatedAt)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>e_entity_0_id</t>
+          <t>e_name_userName</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -727,19 +727,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>${entity_0_id}</t>
+          <t>${gen_test_name('userName')}</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>由 前置 API: display-by-role 提取 (path: entity[0].id)</t>
+          <t>步骤 创建用户 的名称字段</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>e_entity_id</t>
+          <t>e_name_name</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -749,19 +749,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>${entity_id}</t>
+          <t>${gen_test_name('name')}</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>由 前置 API: password-policy 提取 (path: entity.id)</t>
+          <t>步骤 创建用户 的名称字段</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>e_entity_createdAt</t>
+          <t>e_mutable_description</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -771,98 +771,10 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>${entity_createdAt}</t>
+          <t>${gen_mutable_value()}</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
-        <is>
-          <t>由 前置 API: password-policy 提取 (path: entity.createdAt)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>e_entity_updatedAt</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>${entity_updatedAt}</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>由 前置 API: password-policy 提取 (path: entity.updatedAt)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>e_name_userName</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>${gen_test_name('userName')}</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>步骤 创建用户 的名称字段</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>e_name_name</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>${gen_test_name('name')}</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>步骤 创建用户 的名称字段</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>e_mutable_description</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>${gen_mutable_value()}</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
         <is>
           <t>步骤 创建用户 的可变字段</t>
         </is>
